--- a/inst/extdata/cmr-example.xlsx
+++ b/inst/extdata/cmr-example.xlsx
@@ -447,7 +447,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>11400</t>
+          <t>11880</t>
         </is>
       </c>
     </row>
@@ -479,7 +479,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>7600</t>
+          <t>4960</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5800</t>
+          <t>5220</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>4400</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2900</t>
+          <t>2970</t>
         </is>
       </c>
     </row>
